--- a/data/nzd0093/nzd0093.xlsx
+++ b/data/nzd0093/nzd0093.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J327"/>
+  <dimension ref="A1:J328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12212,6 +12212,42 @@
       <c r="J327" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>413.75</v>
+      </c>
+      <c r="C328" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="D328" t="n">
+        <v>369.65</v>
+      </c>
+      <c r="E328" t="n">
+        <v>363.37</v>
+      </c>
+      <c r="F328" t="n">
+        <v>356.57</v>
+      </c>
+      <c r="G328" t="n">
+        <v>356.11</v>
+      </c>
+      <c r="H328" t="n">
+        <v>364.65</v>
+      </c>
+      <c r="I328" t="n">
+        <v>367.55</v>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12226,7 +12262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B340"/>
+  <dimension ref="A1:B341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15629,6 +15665,16 @@
       </c>
       <c r="B340" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -15797,28 +15843,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.343836257292551</v>
+        <v>-0.3453959790695456</v>
       </c>
       <c r="J2" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K2" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03846968424108055</v>
+        <v>0.03905298012705605</v>
       </c>
       <c r="M2" t="n">
-        <v>9.833441348805717</v>
+        <v>9.811989532736638</v>
       </c>
       <c r="N2" t="n">
-        <v>161.27386284173</v>
+        <v>160.8004157790978</v>
       </c>
       <c r="O2" t="n">
-        <v>12.69936466291641</v>
+        <v>12.68071038148486</v>
       </c>
       <c r="P2" t="n">
-        <v>425.510766782376</v>
+        <v>425.527638818245</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15875,28 +15921,28 @@
         <v>0.0622</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1843467534505955</v>
+        <v>-0.1858732666936962</v>
       </c>
       <c r="J3" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K3" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06219534544212002</v>
+        <v>0.06352316446297823</v>
       </c>
       <c r="M3" t="n">
-        <v>3.857273042102823</v>
+        <v>3.85548768307974</v>
       </c>
       <c r="N3" t="n">
-        <v>27.96673541164833</v>
+        <v>27.90012355447991</v>
       </c>
       <c r="O3" t="n">
-        <v>5.288358479873347</v>
+        <v>5.282056754189594</v>
       </c>
       <c r="P3" t="n">
-        <v>375.3471825367886</v>
+        <v>375.3636953447598</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15953,28 +15999,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09946668491737276</v>
+        <v>-0.09867489603841206</v>
       </c>
       <c r="J4" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K4" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03763890443570794</v>
+        <v>0.03729171699117906</v>
       </c>
       <c r="M4" t="n">
-        <v>2.823841142119794</v>
+        <v>2.81819195619937</v>
       </c>
       <c r="N4" t="n">
-        <v>13.80615225204093</v>
+        <v>13.76902005383868</v>
       </c>
       <c r="O4" t="n">
-        <v>3.715663097219786</v>
+        <v>3.710663020787347</v>
       </c>
       <c r="P4" t="n">
-        <v>371.0169879317117</v>
+        <v>371.0084228846864</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16031,28 +16077,28 @@
         <v>0.0675</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05392258656390867</v>
+        <v>-0.05256718172995303</v>
       </c>
       <c r="J5" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K5" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007659292899055092</v>
+        <v>0.007325346280401157</v>
       </c>
       <c r="M5" t="n">
-        <v>3.460522155207078</v>
+        <v>3.455358626970447</v>
       </c>
       <c r="N5" t="n">
-        <v>20.56031900852198</v>
+        <v>20.5123543493739</v>
       </c>
       <c r="O5" t="n">
-        <v>4.534348796522162</v>
+        <v>4.529056673234936</v>
       </c>
       <c r="P5" t="n">
-        <v>362.591277556366</v>
+        <v>362.576615685696</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16109,28 +16155,28 @@
         <v>0.0752</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03711706917902893</v>
+        <v>-0.03658352957986698</v>
       </c>
       <c r="J6" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K6" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002739258349754192</v>
+        <v>0.002678968158099426</v>
       </c>
       <c r="M6" t="n">
-        <v>4.154602170277404</v>
+        <v>4.144684413876693</v>
       </c>
       <c r="N6" t="n">
-        <v>27.37406966848757</v>
+        <v>27.29266738600757</v>
       </c>
       <c r="O6" t="n">
-        <v>5.232023477440403</v>
+        <v>5.224238450339683</v>
       </c>
       <c r="P6" t="n">
-        <v>356.6919736079444</v>
+        <v>356.6862021303724</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16187,28 +16233,28 @@
         <v>0.1169</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.05617702337620114</v>
+        <v>-0.05555157201354061</v>
       </c>
       <c r="J7" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K7" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01272259927443853</v>
+        <v>0.01252437432598486</v>
       </c>
       <c r="M7" t="n">
-        <v>2.697770951345604</v>
+        <v>2.69223522378029</v>
       </c>
       <c r="N7" t="n">
-        <v>13.36586535543086</v>
+        <v>13.32816622364356</v>
       </c>
       <c r="O7" t="n">
-        <v>3.65593563338181</v>
+        <v>3.650776112505882</v>
       </c>
       <c r="P7" t="n">
-        <v>356.5863128868166</v>
+        <v>356.5795471687375</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16265,28 +16311,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01038936507601538</v>
+        <v>0.01079767859104758</v>
       </c>
       <c r="J8" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K8" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003862147001247873</v>
+        <v>0.0004199502748305495</v>
       </c>
       <c r="M8" t="n">
-        <v>2.860510087557752</v>
+        <v>2.853445862954906</v>
       </c>
       <c r="N8" t="n">
-        <v>15.01008828083722</v>
+        <v>14.9652272771325</v>
       </c>
       <c r="O8" t="n">
-        <v>3.874285518755326</v>
+        <v>3.868491602308644</v>
       </c>
       <c r="P8" t="n">
-        <v>363.7160775102462</v>
+        <v>363.7116098574631</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16343,28 +16389,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1265596256405685</v>
+        <v>-0.1252453846840921</v>
       </c>
       <c r="J9" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K9" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04450481626861635</v>
+        <v>0.04387549269551272</v>
       </c>
       <c r="M9" t="n">
-        <v>3.23319350376534</v>
+        <v>3.228949781751195</v>
       </c>
       <c r="N9" t="n">
-        <v>18.76843841749481</v>
+        <v>18.72506157330653</v>
       </c>
       <c r="O9" t="n">
-        <v>4.332255580814088</v>
+        <v>4.327246419295594</v>
       </c>
       <c r="P9" t="n">
-        <v>368.7858151485428</v>
+        <v>368.7715985614019</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -16402,7 +16448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J327"/>
+  <dimension ref="A1:J328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33401,6 +33447,58 @@
         </is>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>-35.63645699503515,174.53043819246417</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>-35.635641763261425,174.53061368157182</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>-35.635142709297035,174.53001042894752</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>-35.63478590010708,174.52925105363104</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-35.634585004724606,174.52838270961</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-35.63462140867846,174.52747854106101</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>-35.63475740492258,174.52659145698507</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-35.63486622945795,174.52570357322725</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0093/nzd0093.xlsx
+++ b/data/nzd0093/nzd0093.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J328"/>
+  <dimension ref="A1:J330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12246,6 +12246,78 @@
         <v>367.55</v>
       </c>
       <c r="J328" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>414.63</v>
+      </c>
+      <c r="C329" t="n">
+        <v>367.39</v>
+      </c>
+      <c r="D329" t="n">
+        <v>368.29</v>
+      </c>
+      <c r="E329" t="n">
+        <v>360.93</v>
+      </c>
+      <c r="F329" t="n">
+        <v>353.36</v>
+      </c>
+      <c r="G329" t="n">
+        <v>353.59</v>
+      </c>
+      <c r="H329" t="n">
+        <v>363.13</v>
+      </c>
+      <c r="I329" t="n">
+        <v>364.71</v>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>414.19</v>
+      </c>
+      <c r="C330" t="n">
+        <v>368.81</v>
+      </c>
+      <c r="D330" t="n">
+        <v>368.35</v>
+      </c>
+      <c r="E330" t="n">
+        <v>361.62</v>
+      </c>
+      <c r="F330" t="n">
+        <v>352.94</v>
+      </c>
+      <c r="G330" t="n">
+        <v>353.78</v>
+      </c>
+      <c r="H330" t="n">
+        <v>362.57</v>
+      </c>
+      <c r="I330" t="n">
+        <v>363.26</v>
+      </c>
+      <c r="J330" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12262,7 +12334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B341"/>
+  <dimension ref="A1:B343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15675,6 +15747,26 @@
       </c>
       <c r="B341" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -15843,28 +15935,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3453959790695456</v>
+        <v>-0.34762644192882</v>
       </c>
       <c r="J2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03905298012705605</v>
+        <v>0.04004535778923402</v>
       </c>
       <c r="M2" t="n">
-        <v>9.811989532736638</v>
+        <v>9.764545975644621</v>
       </c>
       <c r="N2" t="n">
-        <v>160.8004157790978</v>
+        <v>159.8435627229071</v>
       </c>
       <c r="O2" t="n">
-        <v>12.68071038148486</v>
+        <v>12.64292540209374</v>
       </c>
       <c r="P2" t="n">
-        <v>425.527638818245</v>
+        <v>425.5518454989864</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15921,28 +16013,28 @@
         <v>0.0622</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1858732666936962</v>
+        <v>-0.1886159596372205</v>
       </c>
       <c r="J3" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K3" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06352316446297823</v>
+        <v>0.06603433469351649</v>
       </c>
       <c r="M3" t="n">
-        <v>3.85548768307974</v>
+        <v>3.850093392516643</v>
       </c>
       <c r="N3" t="n">
-        <v>27.90012355447991</v>
+        <v>27.76444450515379</v>
       </c>
       <c r="O3" t="n">
-        <v>5.282056754189594</v>
+        <v>5.269197709818241</v>
       </c>
       <c r="P3" t="n">
-        <v>375.3636953447598</v>
+        <v>375.3934551768048</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15999,28 +16091,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09867489603841206</v>
+        <v>-0.09872438567807391</v>
       </c>
       <c r="J4" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K4" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03729171699117906</v>
+        <v>0.03781156176420708</v>
       </c>
       <c r="M4" t="n">
-        <v>2.81819195619937</v>
+        <v>2.801364440488459</v>
       </c>
       <c r="N4" t="n">
-        <v>13.76902005383868</v>
+        <v>13.68533420598488</v>
       </c>
       <c r="O4" t="n">
-        <v>3.710663020787347</v>
+        <v>3.699369433563628</v>
       </c>
       <c r="P4" t="n">
-        <v>371.0084228846864</v>
+        <v>371.0089597581448</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16077,28 +16169,28 @@
         <v>0.0675</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05256718172995303</v>
+        <v>-0.05243127267594876</v>
       </c>
       <c r="J5" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K5" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007325346280401157</v>
+        <v>0.007384960749768243</v>
       </c>
       <c r="M5" t="n">
-        <v>3.455358626970447</v>
+        <v>3.43632066963688</v>
       </c>
       <c r="N5" t="n">
-        <v>20.5123543493739</v>
+        <v>20.3884620946048</v>
       </c>
       <c r="O5" t="n">
-        <v>4.529056673234936</v>
+        <v>4.515358468007252</v>
       </c>
       <c r="P5" t="n">
-        <v>362.576615685696</v>
+        <v>362.5751386741186</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16155,28 +16247,28 @@
         <v>0.0752</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03658352957986698</v>
+        <v>-0.03966557020789219</v>
       </c>
       <c r="J6" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K6" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002678968158099426</v>
+        <v>0.00318557908241246</v>
       </c>
       <c r="M6" t="n">
-        <v>4.144684413876693</v>
+        <v>4.134055287317902</v>
       </c>
       <c r="N6" t="n">
-        <v>27.29266738600757</v>
+        <v>27.16591480658677</v>
       </c>
       <c r="O6" t="n">
-        <v>5.224238450339683</v>
+        <v>5.212093131035436</v>
       </c>
       <c r="P6" t="n">
-        <v>356.6862021303724</v>
+        <v>356.7196502203383</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16233,28 +16325,28 @@
         <v>0.1169</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.05555157201354061</v>
+        <v>-0.05724209072474913</v>
       </c>
       <c r="J7" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K7" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01252437432598486</v>
+        <v>0.01345278624694191</v>
       </c>
       <c r="M7" t="n">
-        <v>2.69223522378029</v>
+        <v>2.685339745470704</v>
       </c>
       <c r="N7" t="n">
-        <v>13.32816622364356</v>
+        <v>13.25890373358089</v>
       </c>
       <c r="O7" t="n">
-        <v>3.650776112505882</v>
+        <v>3.641277761113658</v>
       </c>
       <c r="P7" t="n">
-        <v>356.5795471687375</v>
+        <v>356.5978923976833</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16311,28 +16403,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01079767859104758</v>
+        <v>0.009389662931702538</v>
       </c>
       <c r="J8" t="n">
+        <v>329</v>
+      </c>
+      <c r="K8" t="n">
         <v>327</v>
       </c>
-      <c r="K8" t="n">
-        <v>325</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0004199502748305495</v>
+        <v>0.0003217226455730637</v>
       </c>
       <c r="M8" t="n">
-        <v>2.853445862954906</v>
+        <v>2.843883148774207</v>
       </c>
       <c r="N8" t="n">
-        <v>14.9652272771325</v>
+        <v>14.88212422960032</v>
       </c>
       <c r="O8" t="n">
-        <v>3.868491602308644</v>
+        <v>3.857735635006671</v>
       </c>
       <c r="P8" t="n">
-        <v>363.7116098574631</v>
+        <v>363.7270667545918</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16389,28 +16481,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1252453846840921</v>
+        <v>-0.1269619867020658</v>
       </c>
       <c r="J9" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K9" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04387549269551272</v>
+        <v>0.04557529389973525</v>
       </c>
       <c r="M9" t="n">
-        <v>3.228949781751195</v>
+        <v>3.219005058571883</v>
       </c>
       <c r="N9" t="n">
-        <v>18.72506157330653</v>
+        <v>18.62647284692877</v>
       </c>
       <c r="O9" t="n">
-        <v>4.327246419295594</v>
+        <v>4.315839761498192</v>
       </c>
       <c r="P9" t="n">
-        <v>368.7715985614019</v>
+        <v>368.7902318192142</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -16448,7 +16540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J328"/>
+  <dimension ref="A1:J330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33499,6 +33591,110 @@
         </is>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>-35.636459778628996,174.5304290931494</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>-35.63563926995836,174.53061854385223</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>-35.6351327434372,174.53001917490704</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-35.63476495278206,174.52925927001814</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>-35.63455611764359,174.5283847721527</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>-35.63459876373695,174.52747633866616</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>-35.63474378292406,174.52658964770032</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-35.63484082597137,174.5256996871031</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>-35.63645838683216,174.53043364280686</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>-35.63564607859319,174.5306052660858</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>-35.635133183107506,174.5300187890559</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-35.63477087641091,174.52925694653206</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-35.6345523380255,174.52838504201802</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-35.634600471093655,174.5274765047197</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>-35.634738764293,174.5265889811219</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>-35.63482785588128,174.52569770299147</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0093/nzd0093.xlsx
+++ b/data/nzd0093/nzd0093.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J330"/>
+  <dimension ref="A1:J331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12318,6 +12318,42 @@
         <v>363.26</v>
       </c>
       <c r="J330" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>423.47</v>
+      </c>
+      <c r="C331" t="n">
+        <v>369.9</v>
+      </c>
+      <c r="D331" t="n">
+        <v>368.53</v>
+      </c>
+      <c r="E331" t="n">
+        <v>361.31</v>
+      </c>
+      <c r="F331" t="n">
+        <v>351.94</v>
+      </c>
+      <c r="G331" t="n">
+        <v>354.35</v>
+      </c>
+      <c r="H331" t="n">
+        <v>363.26</v>
+      </c>
+      <c r="I331" t="n">
+        <v>363.7</v>
+      </c>
+      <c r="J331" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12334,7 +12370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B343"/>
+  <dimension ref="A1:B344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15767,6 +15803,16 @@
       </c>
       <c r="B343" t="n">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>-0.43</v>
       </c>
     </row>
   </sheetData>
@@ -15935,28 +15981,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.34762644192882</v>
+        <v>-0.3432344366585657</v>
       </c>
       <c r="J2" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K2" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04004535778923402</v>
+        <v>0.03929314456194477</v>
       </c>
       <c r="M2" t="n">
-        <v>9.764545975644621</v>
+        <v>9.754980308113936</v>
       </c>
       <c r="N2" t="n">
-        <v>159.8435627229071</v>
+        <v>159.5185085029044</v>
       </c>
       <c r="O2" t="n">
-        <v>12.64292540209374</v>
+        <v>12.63006367770584</v>
       </c>
       <c r="P2" t="n">
-        <v>425.5518454989864</v>
+        <v>425.5039853114999</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16013,28 +16059,28 @@
         <v>0.0622</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1886159596372205</v>
+        <v>-0.1888628326313519</v>
       </c>
       <c r="J3" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K3" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06603433469351649</v>
+        <v>0.06660901681344433</v>
       </c>
       <c r="M3" t="n">
-        <v>3.850093392516643</v>
+        <v>3.840035472419869</v>
       </c>
       <c r="N3" t="n">
-        <v>27.76444450515379</v>
+        <v>27.68081320064394</v>
       </c>
       <c r="O3" t="n">
-        <v>5.269197709818241</v>
+        <v>5.261255857743847</v>
       </c>
       <c r="P3" t="n">
-        <v>375.3934551768048</v>
+        <v>375.3961453802671</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16091,28 +16137,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09872438567807391</v>
+        <v>-0.09861771147453055</v>
       </c>
       <c r="J4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03781156176420708</v>
+        <v>0.03797612106955472</v>
       </c>
       <c r="M4" t="n">
-        <v>2.801364440488459</v>
+        <v>2.793289413615277</v>
       </c>
       <c r="N4" t="n">
-        <v>13.68533420598488</v>
+        <v>13.64395748244792</v>
       </c>
       <c r="O4" t="n">
-        <v>3.699369433563628</v>
+        <v>3.693772797892139</v>
       </c>
       <c r="P4" t="n">
-        <v>371.0089597581448</v>
+        <v>371.0077973170576</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16169,28 +16215,28 @@
         <v>0.0675</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05243127267594876</v>
+        <v>-0.05234167907964726</v>
       </c>
       <c r="J5" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K5" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007384960749768243</v>
+        <v>0.007408889336998903</v>
       </c>
       <c r="M5" t="n">
-        <v>3.43632066963688</v>
+        <v>3.426264292876847</v>
       </c>
       <c r="N5" t="n">
-        <v>20.3884620946048</v>
+        <v>20.32674517393536</v>
       </c>
       <c r="O5" t="n">
-        <v>4.515358468007252</v>
+        <v>4.508519177505555</v>
       </c>
       <c r="P5" t="n">
-        <v>362.5751386741186</v>
+        <v>362.5741623623766</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16247,28 +16293,28 @@
         <v>0.0752</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03966557020789219</v>
+        <v>-0.04190477985036042</v>
       </c>
       <c r="J6" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K6" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00318557908241246</v>
+        <v>0.003572385325414151</v>
       </c>
       <c r="M6" t="n">
-        <v>4.134055287317902</v>
+        <v>4.13198518108079</v>
       </c>
       <c r="N6" t="n">
-        <v>27.16591480658677</v>
+        <v>27.12500666102411</v>
       </c>
       <c r="O6" t="n">
-        <v>5.212093131035436</v>
+        <v>5.208167303478653</v>
       </c>
       <c r="P6" t="n">
-        <v>356.7196502203383</v>
+        <v>356.7440511458189</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16325,28 +16371,28 @@
         <v>0.1169</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.05724209072474913</v>
+        <v>-0.05766579069407187</v>
       </c>
       <c r="J7" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K7" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01345278624694191</v>
+        <v>0.01373869487723245</v>
       </c>
       <c r="M7" t="n">
-        <v>2.685339745470704</v>
+        <v>2.679548596706434</v>
       </c>
       <c r="N7" t="n">
-        <v>13.25890373358089</v>
+        <v>13.22020796728953</v>
       </c>
       <c r="O7" t="n">
-        <v>3.641277761113658</v>
+        <v>3.635960391325726</v>
       </c>
       <c r="P7" t="n">
-        <v>356.5978923976833</v>
+        <v>356.6025095050687</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16403,28 +16449,28 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009389662931702538</v>
+        <v>0.008952176862595827</v>
       </c>
       <c r="J8" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K8" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003217226455730637</v>
+        <v>0.0002943919376278137</v>
       </c>
       <c r="M8" t="n">
-        <v>2.843883148774207</v>
+        <v>2.837639847770263</v>
       </c>
       <c r="N8" t="n">
-        <v>14.88212422960032</v>
+        <v>14.83829855540691</v>
       </c>
       <c r="O8" t="n">
-        <v>3.857735635006671</v>
+        <v>3.852051214016619</v>
       </c>
       <c r="P8" t="n">
-        <v>363.7270667545918</v>
+        <v>363.7318885045242</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16481,28 +16527,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1269619867020658</v>
+        <v>-0.1279711066088065</v>
       </c>
       <c r="J9" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K9" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04557529389973525</v>
+        <v>0.04654469845116549</v>
       </c>
       <c r="M9" t="n">
-        <v>3.219005058571883</v>
+        <v>3.214877691142327</v>
       </c>
       <c r="N9" t="n">
-        <v>18.62647284692877</v>
+        <v>18.5784396622464</v>
       </c>
       <c r="O9" t="n">
-        <v>4.315839761498192</v>
+        <v>4.310271413988497</v>
       </c>
       <c r="P9" t="n">
-        <v>368.7902318192142</v>
+        <v>368.801228315111</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -16540,7 +16586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J330"/>
+  <dimension ref="A1:J331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33695,6 +33741,58 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>-35.636487741057095,174.53033768636016</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>-35.635651304938705,174.53059507399587</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>-35.6351345021184,174.53001763150257</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-35.634768215070416,174.52925799041716</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-35.634543338934805,174.5283856845544</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-35.634605593163755,174.52747700288032</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-35.63474494796339,174.52658980244178</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>-35.63483179163276,174.52569830506664</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
